--- a/data/large_test_data.xlsx
+++ b/data/large_test_data.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Faculty" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,20 +12,41 @@
     <sheet name="Rooms" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,16 +66,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -127,41 +171,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -169,6165 +213,6153 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="23.04" customWidth="1" style="2" min="1" max="1"/>
+    <col width="27.94" customWidth="1" style="2" min="2" max="2"/>
+    <col width="41.66" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.23" customWidth="1" style="2" min="4" max="4"/>
+    <col width="24.51" customWidth="1" style="2" min="5" max="5"/>
+    <col width="45.47" customWidth="1" style="2" min="6" max="6"/>
+    <col width="25.36" customWidth="1" style="2" min="7" max="7"/>
+    <col width="33.33" customWidth="1" style="2" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="3">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Employee ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Subjects</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Semesters</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Max Classes Per Day</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Available Days</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="3">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Prof. Rushi</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>EMP001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>CE3015, PH504, PH702, CS2011</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>0, 5, 7</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>kollarushi2006@gmail.com</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Prof. Richard Thomas</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>EMP002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BI505, PH206</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2, 5</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>richard.thomas@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="3">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Prof. Helen Taylor</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>EMP003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>MA1011, MA7013</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Wednesday, Tuesday, Friday, Monday</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>helen.taylor@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="3">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Prof. Richard Martin</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>EMP004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ME3011, BI505, ME608, CH807</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>0, 8, 5, 6</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>richard.martin@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="3">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Dr. Linda Brown</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>EMP005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BI408, CS108, MA405, PH8011</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>0, 1, 4</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>linda.brown@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="3">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Prof. James Harris</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>EMP006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>CE7012, CS804, ME307</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>0, 8, 3</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>james.harris@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="3">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Dr. Michael Thompson</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>EMP007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>PH801, MA703, PH503</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>8, 5, 7</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Monday, Thursday, Wednesday, Friday</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>michael.thompson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="3">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Prof. Sandra Hernandez</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>EMP008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>CE606, MA405, CS607, PH702</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>4, 6, 7</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>sandra.hernandez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="3">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Dr. Robert Wilson</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>EMP009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>PH206, CS607</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2, 6</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>robert.wilson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="3">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Dr. Sharon Moore</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>EMP010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>BI809, CH704, CH709</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>8, 7</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>sharon.moore@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="3">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Dr. Daniel Williams</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>EMP011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>CH807, ME3010, MA6014, BI501</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>8, 0, 5</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>daniel.williams@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="3">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Prof. Maria Jackson</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>EMP012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BI703, PH2013, CS804</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>0, 8, 7</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Monday, Friday, Thursday, Wednesday</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>maria.jackson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="3">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Dr. Robert Jackson</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>EMP013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>MA1011, PH605, ME608</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>0, 6</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>robert.jackson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="3">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Dr. Sharon Lopez</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>EMP014</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>CE3015, ME5012</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>sharon.lopez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="3">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Prof. Nancy Davis</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>EMP015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BI602, CS2015, CH1013</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>0, 6</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>nancy.davis@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="3">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Prof. Sarah Thompson</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>EMP016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>CE7013, BI703</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>0, 7</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>sarah.thompson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="3">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Dr. Ruth Lee</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>EMP017</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ME3010, BI2015, CH803</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>0, 8</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Wednesday, Friday, Thursday, Tuesday</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>ruth.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="3">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Dr. Patricia Taylor</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>EMP018</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>MA606, BI2015</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>0, 6</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>patricia.taylor@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="3">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Dr. Betty Lee</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>EMP019</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>CE301, CE7010</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>0, 3</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>betty.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="3">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Dr. Thomas Davis</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>EMP020</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>CE5014, CS5012</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Tuesday, Thursday, Monday, Wednesday</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>thomas.davis@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Dr. George Harris</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>EMP021</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>CE305, ME2015</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>0, 3</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>george.harris@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Prof. Barbara Gonzalez</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>EMP022</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>MA801, BI602, CH704</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>8, 6, 7</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>barbara.gonzalez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Dr. Sarah Brown</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>EMP023</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>CE802, PH8011, CH108, MA7013</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>8, 0, 1</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>sarah.brown@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Dr. Nancy Lee</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>EMP024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>CH505, CE5011, CS108</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>0, 1, 5</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>nancy.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="3">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Prof. Christopher Thomas</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>EMP025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>CS202, CE708, CH501, CS3013</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>0, 2, 5, 7</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>christopher.thomas@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Dr. Mary Lopez</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>EMP026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>ME703, PH702, CH502</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>5, 7</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>mary.lopez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Dr. Michael Wilson</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>EMP027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>MA703, BI602, CE7010</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>0, 6, 7</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>michael.wilson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Prof. Sharon Lopez</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>EMP028</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>CE807, CS804, ME206</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>8, 2</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>sharon.lopez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Dr. Elizabeth Garcia</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>EMP029</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>CS601, BI1012, PH605</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>0, 6</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Monday, Wednesday, Tuesday, Thursday</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>elizabeth.garcia@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="3">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Dr. Barbara Wilson</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>EMP030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>CS607, CE802</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>8, 6</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>barbara.wilson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="3">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Dr. George White</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>EMP031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>MA807, CE7013, CH5014, PH605</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>8, 0, 6</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>george.white@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33" ht="15" customHeight="1" s="3">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Dr. Susan Williams</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>EMP032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>PH208, MA7013, CE305</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>0, 2, 3</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>susan.williams@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="3">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Dr. Lisa Davis</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>EMP033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BI2011, CE7012</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>lisa.davis@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="3">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Dr. Susan Moore</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>EMP034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>PH208, PH206, ME608, PH1014</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>0, 2, 6</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>susan.moore@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="3">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Dr. Sarah Davis</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>EMP035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>CE5014, CE5011, PH208</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>0, 2</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Wednesday, Thursday, Tuesday, Friday</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>sarah.davis@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="3">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Dr. Maria Lee</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>EMP036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>MA6014, PH801, MA807</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>0, 8</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>maria.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="15" customHeight="1" s="3">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Prof. Daniel Gonzalez</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>EMP037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>ME601, MA1011, PH605, CS202</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>0, 2, 6</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>daniel.gonzalez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="3">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Dr. Donald Lee</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>EMP038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>MA801, CH704, PH801</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>8, 7</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Monday, Friday, Wednesday, Thursday</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>donald.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" ht="15" customHeight="1" s="3">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Dr. Jennifer Davis</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>EMP039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BI703, ME7013</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>0, 7</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>jennifer.davis@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="3">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Prof. Helen Lee</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>EMP040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>CH1012, PH208, CS4014, MA703</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>0, 2, 7</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>helen.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="3">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Prof. Joseph Anderson</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>EMP041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>ME7013, PH702, CH1012, CH505</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>0, 5, 7</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>joseph.anderson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="3">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Prof. Maria Smith</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>EMP042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>CE301, CS809</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>8, 3</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Friday, Tuesday, Monday, Wednesday</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Civil Engineering</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>maria.smith@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="3">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Dr. Maria Garcia</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>EMP043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>CE802, CS108, PH707</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>8, 1, 7</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>maria.garcia@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="3">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Prof. Christopher Williams</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>EMP044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>CS503, CS2011</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>0, 5</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>christopher.williams@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="3">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Prof. George Wilson</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>EMP045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>CE5014, CE7010, MA807, BI2011</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>0, 8</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Monday, Thursday, Tuesday, Wednesday</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>george.wilson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="3">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Dr. Emily Garcia</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>EMP046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BI501, CS2015, CE5014, CH505</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>0, 5</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>emily.garcia@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="3">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Prof. Helen Moore</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>EMP047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>ME304, MA6012, BI703, MA801</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>0, 8, 3, 7</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>helen.moore@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Dr. William Lee</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>EMP048</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BI6014, BI206</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>0, 2</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Chemistry</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>william.lee@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="50" ht="15" customHeight="1" s="3">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Prof. Linda Anderson</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>EMP049</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>MA801, CS607, BI6014, PH8011</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>8, 0, 6</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>linda.anderson@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="51" ht="15" customHeight="1" s="3">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Prof. John Martinez</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>EMP050</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BI504, CE7013</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>0, 5</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>john.martinez@vyuha-college.edu</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="52" ht="15" customHeight="1" s="3">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>manik</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>EMP101</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>CS601, CS202, CS503, CS804, CS607</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2, 5, 6, 8</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>mpadake.01@gmail.com</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="3">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>edrfd</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>EMP102</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>CS601, CS202, CS503, CS804, CS607</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2, 5, 6, 8</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>dizolay@gmail.com</t>
         </is>
       </c>
     </row>
+    <row r="54" ht="15" customHeight="1" s="3">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>redev</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>EMB005</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>CS108, CS202, CS601, CS804</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Friday, Tuesday, Monday, Wednesday</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>mounishmuniraju0228@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>redev</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>EMP_REDEV_001</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Computer Science, AI, Web Dev</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday, Saturday</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>mounishmuniraju0228@gmail.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:E106"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="3">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Classes Per Week</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Room Type Required</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Duration Minutes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="15" customHeight="1" s="3">
+      <c r="A2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CS601</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="3">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CS202</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="3">
+      <c r="A4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>CS503</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="15" customHeight="1" s="3">
+      <c r="A5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>CS804</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="15" customHeight="1" s="3">
+      <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CS805</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="15" customHeight="1" s="3">
+      <c r="A7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CS506</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="3">
+      <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CS607</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="15" customHeight="1" s="3">
+      <c r="A9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CS108</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="3">
+      <c r="A10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CS809</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="15" customHeight="1" s="3">
+      <c r="A11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CS6010</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="3">
+      <c r="A12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CS2011</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="3">
+      <c r="A13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CS5012</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" ht="15" customHeight="1" s="3">
+      <c r="A14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CS3013</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" ht="15" customHeight="1" s="3">
+      <c r="A15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CS4014</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="3">
+      <c r="A16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CS2015</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="3">
+      <c r="A17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>MA801</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" ht="15" customHeight="1" s="3">
+      <c r="A18" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>MA802</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="3">
+      <c r="A19" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>MA703</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="3">
+      <c r="A20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>MA504</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="3">
+      <c r="A21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>MA405</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>MA606</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>MA807</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>MA408</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>MA109</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="3">
+      <c r="A26" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>MA6010</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>MA1011</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>MA6012</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>MA7013</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>MA6014</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="3">
+      <c r="A31" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>MA7015</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="3">
+      <c r="A32" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>PH801</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" ht="15" customHeight="1" s="3">
+      <c r="A33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>PH702</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="3">
+      <c r="A34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PH503</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" ht="15" customHeight="1" s="3">
+      <c r="A35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>PH504</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="3">
+      <c r="A36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PH605</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="3">
+      <c r="A37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>PH206</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="3">
+      <c r="A38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>PH707</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" ht="15" customHeight="1" s="3">
+      <c r="A39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>PH208</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="3">
+      <c r="A40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>PH709</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="3">
+      <c r="A41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>PH5010</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="3">
+      <c r="A42" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>PH8011</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="3">
+      <c r="A43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>PH1012</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" ht="15" customHeight="1" s="3">
+      <c r="A44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>PH2013</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="3">
+      <c r="A45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PH1014</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="3">
+      <c r="A46" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PH8015</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" ht="15" customHeight="1" s="3">
+      <c r="A47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>CH501</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" ht="15" customHeight="1" s="3">
+      <c r="A48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>CH502</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>CH803</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="3">
+      <c r="A50" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>CH704</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" ht="15" customHeight="1" s="3">
+      <c r="A51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>CH505</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="3">
+      <c r="A52" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CH606</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="3">
+      <c r="A53" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>CH807</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="3">
+      <c r="A54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>CH108</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="3">
+      <c r="A55" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>CH709</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" ht="15" customHeight="1" s="3">
+      <c r="A56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>CH6010</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" ht="15" customHeight="1" s="3">
+      <c r="A57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>CH3011</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="3">
+      <c r="A58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>CH1012</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="3">
+      <c r="A59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>CH1013</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="3">
+      <c r="A60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>CH5014</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="3">
+      <c r="A61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>CH5015</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" ht="15" customHeight="1" s="3">
+      <c r="A62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>BI501</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="3">
+      <c r="A63" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>BI602</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="3">
+      <c r="A64" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>BI703</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="3">
+      <c r="A65" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>BI504</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="3">
+      <c r="A66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>BI505</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="3">
+      <c r="A67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>BI206</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="3">
+      <c r="A68" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>BI407</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="3">
+      <c r="A69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>BI408</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" ht="15" customHeight="1" s="3">
+      <c r="A70" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>BI809</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" ht="15" customHeight="1" s="3">
+      <c r="A71" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>BI7010</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="3">
+      <c r="A72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>BI2011</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="3">
+      <c r="A73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>BI1012</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="3">
+      <c r="A74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>BI6013</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="3">
+      <c r="A75" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>BI6014</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="3">
+      <c r="A76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>BI2015</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="3">
+      <c r="A77" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>ME601</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="3">
+      <c r="A78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>ME302</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" ht="15" customHeight="1" s="3">
+      <c r="A79" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>ME703</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" ht="15" customHeight="1" s="3">
+      <c r="A80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>ME304</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="3">
+      <c r="A81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>ME505</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" ht="15" customHeight="1" s="3">
+      <c r="A82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>ME206</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" ht="15" customHeight="1" s="3">
+      <c r="A83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>ME307</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="3">
+      <c r="A84" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>ME608</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="3">
+      <c r="A85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>ME109</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" ht="15" customHeight="1" s="3">
+      <c r="A86" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>ME3010</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="3">
+      <c r="A87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>ME3011</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" ht="15" customHeight="1" s="3">
+      <c r="A88" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>ME5012</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="3">
+      <c r="A89" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>ME7013</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="3">
+      <c r="A90" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>ME8014</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" ht="15" customHeight="1" s="3">
+      <c r="A91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>ME2015</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="3">
+      <c r="A92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>CE301</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="3">
+      <c r="A93" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>CE802</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="3">
+      <c r="A94" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>CE303</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="3">
+      <c r="A95" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>CE404</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="3">
+      <c r="A96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>CE305</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="3">
+      <c r="A97" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>CE606</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="2" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" ht="15" customHeight="1" s="3">
+      <c r="A98" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>CE807</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="3">
+      <c r="A99" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>CE708</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="3">
+      <c r="A100" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>CE709</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="3">
+      <c r="A101" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>CE7010</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="3">
+      <c r="A102" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>CE5011</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="3">
+      <c r="A103" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>CE7012</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="3">
+      <c r="A104" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>CE7013</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="3">
+      <c r="A105" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>CE5014</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="3">
+      <c r="A106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>CE3015</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:E61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="3">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Room Code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Room Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Room Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Available Days</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="3">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>A101</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Hall A101</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>A102</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Hall A102</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="3">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>A103</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Hall A103</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="3">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>A104</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Lab A104</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="3">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>A105</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hall A105</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="3">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>A201</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Hall A201</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="3">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A202</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Hall A202</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="3">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>A203</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Lab A203</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="3">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A204</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Hall A204</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="3">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>A205</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Hall A205</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="3">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>A301</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Hall A301</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>60</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="3">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>A302</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Lab A302</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="3">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>A303</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Hall A303</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="3">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>A304</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Hall A304</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="3">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>A305</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Hall A305</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="3">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>B101</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Lab B101</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="3">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>B102</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Hall B102</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="3">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>B103</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Hall B103</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="3">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>B104</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Hall B104</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="3">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>B105</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Lab B105</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>B201</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Hall B201</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>B202</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Hall B202</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>B203</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Hall B203</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>B204</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Lab B204</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="3">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>B205</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Hall B205</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>B301</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Hall B301</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>B302</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Hall B302</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>60</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="C28" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>B303</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Lab B303</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>B304</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Hall B304</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="3">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>B305</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Hall B305</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="3">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C101</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Hall C101</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>60</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="C32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="3">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>C102</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Lab C102</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="3">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C103</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Hall C103</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>60</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="C34" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="3">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>C104</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Hall C104</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="3">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C105</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Hall C105</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="3">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>C201</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Lab C201</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="3">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C202</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Hall C202</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>60</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="C38" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="3">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>C203</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Hall C203</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>60</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="C39" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="3">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C204</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Hall C204</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="3">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>C205</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Lab C205</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="3">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C301</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Hall C301</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="3">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>C302</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Hall C302</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="3">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C303</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Hall C303</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>60</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="C44" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="3">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>C304</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Lab C304</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="3">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C305</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Hall C305</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>60</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="C46" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="3">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>D101</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Hall D101</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="3">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>D102</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Hall D102</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>D103</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Lab D103</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="3">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>D104</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Hall D104</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="3">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>D105</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Hall D105</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="3">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>D201</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Hall D201</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="3">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>D202</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Lab D202</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="3">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>D203</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Hall D203</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="3">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>D204</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Hall D204</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="3">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>D205</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Hall D205</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>60</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="C56" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="3">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>D301</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Lab D301</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="3">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>D302</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Hall D302</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="3">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>D303</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Hall D303</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="3">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>D304</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Hall D304</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Theory</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="3">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>D305</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Lab D305</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Monday, Tuesday, Wednesday, Thursday, Friday</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>